--- a/wooclap/imports/08_Intro_ML_Part_2.xlsx
+++ b/wooclap/imports/08_Intro_ML_Part_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$4</definedName>

--- a/wooclap/imports/08_Intro_ML_Part_2.xlsx
+++ b/wooclap/imports/08_Intro_ML_Part_2.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L03-C05 · A table has one row per house and columns for area, number of rooms and price. Which column is the target when predicting price?</t>
+          <t>L03-C05 · 60 field trials record fertilizer and soil moisture to predict yield. A trial ID is kept only for lookup. With one row per trial, which input/target representation is correct?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Area.</t>
+          <t>X has shape 60×3 because the lookup ID must also be a predictor; Y has 60 entries.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Price.</t>
+          <t>X has shape 60×2 for the two predictors; Y has the 60 measured yields.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Number of rooms.</t>
+          <t>X has shape 2×60 and Y has two entries, one per predictor.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The row number.</t>
+          <t>X has shape 60×3 including measured yield; Y repeats that same yield column.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L03-C06 · You want a fair test of whether a student can solve new exercises. Which set should you use for the test?</t>
+          <t>L03-C06 · An engineer computes a feature mean from all 1,000 rows, uses it to scale the inputs, and only then splits into training and test sets. Test targets never enter fitting. Is the final test independent of model preparation?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Only the exercises they have memorized.</t>
+          <t>Yes: preprocessing cannot leak information unless it uses test targets.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>The practice sheet with the answers printed next to each question.</t>
+          <t>Yes: a random split makes every earlier preparation step independent.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Whichever practice exercises gave the highest score.</t>
+          <t>Yes, provided the best model is also selected using the test score.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Exercises the student has not already practiced or used to choose a strategy.</t>
+          <t>No: test inputs influenced learned preprocessing; fit that preprocessing on training data only.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L03-C07 · Why do we test a machine-learning model on examples it did not learn from? Answer in one sentence.</t>
+          <t>L03-C07 · Two polynomial models have training/validation errors: degree 2 = (0.08, 0.10), degree 9 = (0.01, 0.35). Choose a model for new fields, justify your choice, and say which data should provide the final performance estimate.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
